--- a/registration_forms/035_stage_production_crew_registration_form--registration_forms.xlsx
+++ b/registration_forms/035_stage_production_crew_registration_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1133,7 +1133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1506,29 +1506,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>green_room</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Green Room</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>stage_production_crew_registration_form_venue_choices</t>
+          <t>stage_production_crew_registration_form_stage_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>front_of_house</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Front of House</t>
         </is>
       </c>
     </row>
@@ -1540,12 +1540,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>front_of_house</t>
+          <t>back_of_house</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Front of House</t>
+          <t>Back of House</t>
         </is>
       </c>
     </row>
@@ -1557,12 +1557,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>back_of_house</t>
+          <t>stage</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Back of House</t>
+          <t>Stage</t>
         </is>
       </c>
     </row>
@@ -1574,29 +1574,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>stage</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Stage</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>stage_production_crew_registration_form_stage_choices</t>
+          <t>stage_production_crew_registration_form_backstage_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>front_of_house</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Front of House</t>
         </is>
       </c>
     </row>
@@ -1608,12 +1608,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>front_of_house</t>
+          <t>back_of_house</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Front of House</t>
+          <t>Back of House</t>
         </is>
       </c>
     </row>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>back_of_house</t>
+          <t>stage</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Back of House</t>
+          <t>Stage</t>
         </is>
       </c>
     </row>
@@ -1642,29 +1642,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>stage</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Stage</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>stage_production_crew_registration_form_backstage_choices</t>
+          <t>stage_production_crew_registration_form_front_of_house_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1676,29 +1676,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>stage_production_crew_registration_form_front_of_house_choices</t>
+          <t>stage_production_crew_registration_form_back_of_house_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1710,29 +1710,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>stage_production_crew_registration_form_back_of_house_choices</t>
+          <t>stage_production_crew_registration_form_stage_equipment_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1744,27 +1744,10 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>stage_production_crew_registration_form_stage_equipment_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
         <is>
           <t>False</t>
         </is>
